--- a/outputs/formato_input_catalog_control_center_brand_basico_handle_20260720.xlsx
+++ b/outputs/formato_input_catalog_control_center_brand_basico_handle_20260720.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPUT_COMERCIAL" sheetId="1" r:id="Ra38dce4017a74eb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DICCIONARIO_COLUMNAS" sheetId="2" r:id="R8ed2565e717240f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIPOS_PRENDA" sheetId="3" r:id="R71a1f937efdc4b40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUIAS_TALLA" sheetId="4" r:id="R4d927292f1b04252"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATEGORIAS" sheetId="5" r:id="R4d3e23983c4a4872"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALORES_PERMITIDOS" sheetId="6" r:id="R46b64637b81d4f3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERRORES_Y_ADVERTENCIAS" sheetId="7" r:id="Rb130d8d0394a4834"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPUT_COMERCIAL" sheetId="1" r:id="R1d5e45306d944a60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DICCIONARIO_COLUMNAS" sheetId="2" r:id="R2b49714f67a94d2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIPOS_PRENDA" sheetId="3" r:id="R08b199c1dc0c4628"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUIAS_TALLA" sheetId="4" r:id="R29abed733301415e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATEGORIAS" sheetId="5" r:id="R9932a7771e9842fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALORES_PERMITIDOS" sheetId="6" r:id="R15c01aeed0bf4140"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERRORES_Y_ADVERTENCIAS" sheetId="7" r:id="R4c074ce3d2ac44d7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -367,8 +367,8 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="29.1299991607666" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="17.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="50.5" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="50.5" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="11.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="24.3799991607666" hidden="0" customWidth="1"/>
@@ -381,17 +381,17 @@
     <x:col min="13" max="13" width="27.5" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="20.75" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="24.5" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="17" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="28" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="13.5" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="9.25" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="16.3799991607666" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="19.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="57" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="48.630001068115234" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="36.25" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="62.25" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="38.25" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="31.6299991607666" hidden="0" customWidth="1"/>
     <x:col min="22" max="22" width="18.6299991607666" hidden="0" customWidth="1"/>
     <x:col min="23" max="23" width="23" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="23.8799991607666" hidden="0" customWidth="1"/>
-    <x:col min="25" max="25" width="27.3799991607666" hidden="0" customWidth="1"/>
-    <x:col min="26" max="26" width="38.25" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="43.25" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="56.630001068115234" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="59" hidden="0" customWidth="1"/>
     <x:col min="27" max="27" width="15.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="28" max="28" width="19.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="29" max="29" width="16.1299991607666" hidden="0" customWidth="1"/>
@@ -563,7 +563,7 @@
         <x:v>Columbia, Vestuario, Mujer, Casacas</x:v>
       </x:c>
       <x:c r="Z2" s="8" t="str">
-        <x:v>casaca-impermeable-mujer-arcadia-ii-2092991-nry</x:v>
+        <x:v>casacas-mujer-columbia-2092991-nry</x:v>
       </x:c>
       <x:c r="AA2" s="8" t="str"/>
       <x:c r="AB2" s="8" t="str"/>
@@ -577,10 +577,10 @@
         <x:v>Codigo modelo-color. Ej: 2092991-NRY</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
-        <x:v>Modelo sin color.</x:v>
+        <x:v>La app lo puede obtener desde Mod-Col/ARTI. No lo llena la marca.</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>Codigo de color fuente.</x:v>
+        <x:v>La app lo puede obtener desde Mod-Col/ARTI. No lo llena la marca.</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
         <x:v>Marca destino.</x:v>
@@ -619,22 +619,22 @@
         <x:v>Instrucciones de cuidado.</x:v>
       </x:c>
       <x:c r="P3" s="9" t="str">
-        <x:v>Talla real. No inventar.</x:v>
+        <x:v>La app la obtiene desde BigQuery/ARTI. No inventar ni cargar tallas teoricas.</x:v>
       </x:c>
       <x:c r="Q3" s="9" t="str">
-        <x:v>Cod Int/SKU obligatorio por variante.</x:v>
+        <x:v>La app lo obtiene desde BigQuery/ARTI. Obligatorio por variante.</x:v>
       </x:c>
       <x:c r="R3" s="9" t="str">
-        <x:v>Codigo de barras.</x:v>
+        <x:v>La app lo obtiene desde BigQuery/ARTI si existe.</x:v>
       </x:c>
       <x:c r="S3" s="9" t="str">
-        <x:v>Precio final.</x:v>
+        <x:v>La app lo obtiene desde Shopify/ARTI si existe; la marca solo completa si se solicita.</x:v>
       </x:c>
       <x:c r="T3" s="9" t="str">
-        <x:v>Precio antes si aplica.</x:v>
+        <x:v>Precio antes si aplica desde fuente comercial/ARTI.</x:v>
       </x:c>
       <x:c r="U3" s="9" t="str">
-        <x:v>Stock eComm referencial.</x:v>
+        <x:v>Stock eComm referencial desde BigQuery.</x:v>
       </x:c>
       <x:c r="V3" s="9" t="str">
         <x:v>Separar por coma.</x:v>
@@ -643,13 +643,13 @@
         <x:v>Nombre o GID de metaobjeto.</x:v>
       </x:c>
       <x:c r="X3" s="9" t="str">
-        <x:v>Guia Shopify si viene aprobada.</x:v>
+        <x:v>La app la resuelve por categoria, tipo de prenda y genero.</x:v>
       </x:c>
       <x:c r="Y3" s="9" t="str">
-        <x:v>Tags separados por coma.</x:v>
+        <x:v>La app los sugiere con marca, categoria, genero, tipo, tecnologia y Mod-Col.</x:v>
       </x:c>
       <x:c r="Z3" s="9" t="str">
-        <x:v>Handle sugerido.</x:v>
+        <x:v>No llenar manualmente. Formula: tipo de prenda + genero + marca + Mod-Col.</x:v>
       </x:c>
       <x:c r="AA3" s="9" t="str">
         <x:v>Titulo SEO opcional.</x:v>
@@ -2189,10 +2189,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="13.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22.5" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="9.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="29.1299991607666" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="38.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="62.25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="33.630001068115234" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="14.5" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="23.6299991607666" hidden="0" customWidth="1"/>
   </x:cols>
@@ -2248,13 +2248,13 @@
         <x:v>Codigo modelo</x:v>
       </x:c>
       <x:c r="B3" s="13" t="str">
-        <x:v>Identificacion</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C3" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
-        <x:v>Modelo sin color.</x:v>
+        <x:v>La app lo puede obtener desde Mod-Col/ARTI. No lo llena la marca.</x:v>
       </x:c>
       <x:c r="E3" s="13" t="str">
         <x:v>2092991</x:v>
@@ -2271,13 +2271,13 @@
         <x:v>Codigo color</x:v>
       </x:c>
       <x:c r="B4" s="13" t="str">
-        <x:v>Identificacion</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C4" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
-        <x:v>Codigo de color fuente.</x:v>
+        <x:v>La app lo puede obtener desde Mod-Col/ARTI. No lo llena la marca.</x:v>
       </x:c>
       <x:c r="E4" s="13" t="str">
         <x:v>NRY</x:v>
@@ -2568,13 +2568,13 @@
         <x:v>Talla</x:v>
       </x:c>
       <x:c r="B17" s="13" t="str">
-        <x:v>Variantes y tallas</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C17" s="13" t="str">
         <x:v>SI</x:v>
       </x:c>
       <x:c r="D17" s="13" t="str">
-        <x:v>Talla real. No inventar.</x:v>
+        <x:v>La app la obtiene desde BigQuery/ARTI. No inventar ni cargar tallas teoricas.</x:v>
       </x:c>
       <x:c r="E17" s="13" t="str">
         <x:v>M</x:v>
@@ -2591,13 +2591,13 @@
         <x:v>SKU</x:v>
       </x:c>
       <x:c r="B18" s="13" t="str">
-        <x:v>Variantes y tallas</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C18" s="13" t="str">
         <x:v>SI</x:v>
       </x:c>
       <x:c r="D18" s="13" t="str">
-        <x:v>Cod Int/SKU obligatorio por variante.</x:v>
+        <x:v>La app lo obtiene desde BigQuery/ARTI. Obligatorio por variante.</x:v>
       </x:c>
       <x:c r="E18" s="13" t="str">
         <x:v>5327440</x:v>
@@ -2614,13 +2614,13 @@
         <x:v>EAN</x:v>
       </x:c>
       <x:c r="B19" s="13" t="str">
-        <x:v>Variantes y tallas</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C19" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D19" s="13" t="str">
-        <x:v>Codigo de barras.</x:v>
+        <x:v>La app lo obtiene desde BigQuery/ARTI si existe.</x:v>
       </x:c>
       <x:c r="E19" s="13" t="str">
         <x:v>7800000000000</x:v>
@@ -2637,13 +2637,13 @@
         <x:v>Precio</x:v>
       </x:c>
       <x:c r="B20" s="13" t="str">
-        <x:v>Precios</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C20" s="13" t="str">
         <x:v>SI</x:v>
       </x:c>
       <x:c r="D20" s="13" t="str">
-        <x:v>Precio final.</x:v>
+        <x:v>La app lo obtiene desde Shopify/ARTI si existe; la marca solo completa si se solicita.</x:v>
       </x:c>
       <x:c r="E20" s="13" t="str">
         <x:v>299.90</x:v>
@@ -2660,13 +2660,13 @@
         <x:v>Compare At Price</x:v>
       </x:c>
       <x:c r="B21" s="13" t="str">
-        <x:v>Precios</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C21" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D21" s="13" t="str">
-        <x:v>Precio antes si aplica.</x:v>
+        <x:v>Precio antes si aplica desde fuente comercial/ARTI.</x:v>
       </x:c>
       <x:c r="E21" s="13" t="str"/>
       <x:c r="F21" s="13" t="str">
@@ -2681,13 +2681,13 @@
         <x:v>Stock disponible</x:v>
       </x:c>
       <x:c r="B22" s="13" t="str">
-        <x:v>Inventario</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C22" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D22" s="13" t="str">
-        <x:v>Stock eComm referencial.</x:v>
+        <x:v>Stock eComm referencial desde BigQuery.</x:v>
       </x:c>
       <x:c r="E22" s="13" t="str">
         <x:v>12</x:v>
@@ -2750,13 +2750,13 @@
         <x:v>Guia de tallas</x:v>
       </x:c>
       <x:c r="B25" s="13" t="str">
-        <x:v>Guia de talla</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C25" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D25" s="13" t="str">
-        <x:v>Guia Shopify si viene aprobada.</x:v>
+        <x:v>La app la resuelve por categoria, tipo de prenda y genero.</x:v>
       </x:c>
       <x:c r="E25" s="13" t="str">
         <x:v>CLB_MUJER_TOPS</x:v>
@@ -2773,13 +2773,13 @@
         <x:v>Tags sugeridos</x:v>
       </x:c>
       <x:c r="B26" s="13" t="str">
-        <x:v>SEO y tags</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C26" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D26" s="13" t="str">
-        <x:v>Tags separados por coma.</x:v>
+        <x:v>La app los sugiere con marca, categoria, genero, tipo, tecnologia y Mod-Col.</x:v>
       </x:c>
       <x:c r="E26" s="13" t="str">
         <x:v>Columbia, Vestuario, Mujer, Casacas</x:v>
@@ -2796,16 +2796,16 @@
         <x:v>Handle sugerido</x:v>
       </x:c>
       <x:c r="B27" s="13" t="str">
-        <x:v>SEO y tags</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C27" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D27" s="13" t="str">
-        <x:v>Handle sugerido.</x:v>
+        <x:v>No llenar manualmente. Formula: tipo de prenda + genero + marca + Mod-Col.</x:v>
       </x:c>
       <x:c r="E27" s="13" t="str">
-        <x:v>casaca-impermeable-mujer-arcadia-ii-2092991-nry</x:v>
+        <x:v>casacas-mujer-columbia-2092991-nry</x:v>
       </x:c>
       <x:c r="F27" s="13" t="str">
         <x:v>Producto / reporte</x:v>
@@ -2909,13 +2909,13 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="21" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22.1299991607666" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="14.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="15.75" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="8.5" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="10.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="9.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="15.5" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="13.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="21" hidden="0" customWidth="1"/>
   </x:cols>
@@ -2998,7 +2998,7 @@
         <x:v>Casacas</x:v>
       </x:c>
       <x:c r="G3" s="13" t="str">
-        <x:v>Vestuario</x:v>
+        <x:v>Vestuario TOPS</x:v>
       </x:c>
       <x:c r="H3" s="13" t="str">
         <x:v>NO</x:v>
@@ -3027,7 +3027,7 @@
         <x:v>Polos</x:v>
       </x:c>
       <x:c r="G4" s="13" t="str">
-        <x:v>Vestuario</x:v>
+        <x:v>Vestuario TOPS</x:v>
       </x:c>
       <x:c r="H4" s="13" t="str">
         <x:v>NO</x:v>
@@ -3038,117 +3038,175 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="13" t="str">
-        <x:v>gorro, beanie, jockey</x:v>
+        <x:v>pantalon, pants, jogger</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>Gorro</x:v>
+        <x:v>Pantalon</x:v>
       </x:c>
       <x:c r="C5" s="13" t="str">
-        <x:v>Gorro</x:v>
+        <x:v>Pantalon</x:v>
       </x:c>
       <x:c r="D5" s="13" t="str">
-        <x:v>Gorros</x:v>
+        <x:v>Pantalones</x:v>
       </x:c>
       <x:c r="E5" s="13" t="str">
-        <x:v>Accesorios</x:v>
+        <x:v>Vestuario</x:v>
       </x:c>
       <x:c r="F5" s="13" t="str">
-        <x:v>Gorros</x:v>
+        <x:v>Pantalones</x:v>
       </x:c>
       <x:c r="G5" s="13" t="str">
-        <x:v>Accesorios</x:v>
+        <x:v>Vestuario BOTTOMS</x:v>
       </x:c>
       <x:c r="H5" s="13" t="str">
-        <x:v>SI</x:v>
+        <x:v>NO</x:v>
       </x:c>
       <x:c r="I5" s="13" t="str">
-        <x:v>Gorro Cachalot</x:v>
+        <x:v>Pantalon Trekking Mujer</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="13" t="str">
-        <x:v>mochila, bolso, cartera, bag</x:v>
+        <x:v>short, shorts, bermuda, falda</x:v>
       </x:c>
       <x:c r="B6" s="13" t="str">
-        <x:v>Bolso</x:v>
+        <x:v>Short</x:v>
       </x:c>
       <x:c r="C6" s="13" t="str">
-        <x:v>Bolso</x:v>
+        <x:v>Short</x:v>
       </x:c>
       <x:c r="D6" s="13" t="str">
-        <x:v>Bolsos</x:v>
+        <x:v>Shorts</x:v>
       </x:c>
       <x:c r="E6" s="13" t="str">
-        <x:v>Accesorios</x:v>
+        <x:v>Vestuario</x:v>
       </x:c>
       <x:c r="F6" s="13" t="str">
-        <x:v>Bolsos</x:v>
+        <x:v>Shorts</x:v>
       </x:c>
       <x:c r="G6" s="13" t="str">
-        <x:v>Accesorios</x:v>
+        <x:v>Vestuario BOTTOMS</x:v>
       </x:c>
       <x:c r="H6" s="13" t="str">
-        <x:v>SI</x:v>
+        <x:v>NO</x:v>
       </x:c>
       <x:c r="I6" s="13" t="str">
-        <x:v>Bolso Outdoor</x:v>
+        <x:v>Short Hombre Outdoor</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="13" t="str">
-        <x:v>slip on, slip-on</x:v>
+        <x:v>gorro, beanie, jockey</x:v>
       </x:c>
       <x:c r="B7" s="13" t="str">
-        <x:v>Slip On</x:v>
+        <x:v>Gorro</x:v>
       </x:c>
       <x:c r="C7" s="13" t="str">
-        <x:v>Slip On</x:v>
+        <x:v>Gorro</x:v>
       </x:c>
       <x:c r="D7" s="13" t="str">
-        <x:v>Slip Ons</x:v>
+        <x:v>Gorros</x:v>
       </x:c>
       <x:c r="E7" s="13" t="str">
-        <x:v>Calzado</x:v>
+        <x:v>Accesorios</x:v>
       </x:c>
       <x:c r="F7" s="13" t="str">
-        <x:v>Slip Ons</x:v>
+        <x:v>Gorros</x:v>
       </x:c>
       <x:c r="G7" s="13" t="str">
-        <x:v>Calzado</x:v>
+        <x:v>Accesorios</x:v>
       </x:c>
       <x:c r="H7" s="13" t="str">
-        <x:v>NO</x:v>
+        <x:v>SI</x:v>
       </x:c>
       <x:c r="I7" s="13" t="str">
-        <x:v>Slip On Vans</x:v>
+        <x:v>Gorro Cachalot</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="13" t="str">
-        <x:v>crema renovadora, cleaner</x:v>
+        <x:v>mochila, bolso, cartera, bag</x:v>
       </x:c>
       <x:c r="B8" s="13" t="str">
-        <x:v>Crema renovadora</x:v>
+        <x:v>Bolso</x:v>
       </x:c>
       <x:c r="C8" s="13" t="str">
-        <x:v>Crema renovadora</x:v>
+        <x:v>Bolso</x:v>
       </x:c>
       <x:c r="D8" s="13" t="str">
-        <x:v>Cremas renovadoras</x:v>
+        <x:v>Bolsos</x:v>
       </x:c>
       <x:c r="E8" s="13" t="str">
         <x:v>Accesorios</x:v>
       </x:c>
       <x:c r="F8" s="13" t="str">
-        <x:v>Cuidado</x:v>
+        <x:v>Bolsos</x:v>
       </x:c>
       <x:c r="G8" s="13" t="str">
-        <x:v>Sin guia</x:v>
+        <x:v>Accesorios</x:v>
       </x:c>
       <x:c r="H8" s="13" t="str">
         <x:v>SI</x:v>
       </x:c>
       <x:c r="I8" s="13" t="str">
+        <x:v>Bolso Outdoor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="13" t="str">
+        <x:v>slip on, slip-on</x:v>
+      </x:c>
+      <x:c r="B9" s="13" t="str">
+        <x:v>Slip On</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="str">
+        <x:v>Slip On</x:v>
+      </x:c>
+      <x:c r="D9" s="13" t="str">
+        <x:v>Slip Ons</x:v>
+      </x:c>
+      <x:c r="E9" s="13" t="str">
+        <x:v>Calzado</x:v>
+      </x:c>
+      <x:c r="F9" s="13" t="str">
+        <x:v>Slip Ons</x:v>
+      </x:c>
+      <x:c r="G9" s="13" t="str">
+        <x:v>Calzado</x:v>
+      </x:c>
+      <x:c r="H9" s="13" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="I9" s="13" t="str">
+        <x:v>Slip On Vans</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="13" t="str">
+        <x:v>crema renovadora, cleaner</x:v>
+      </x:c>
+      <x:c r="B10" s="13" t="str">
+        <x:v>Crema renovadora</x:v>
+      </x:c>
+      <x:c r="C10" s="13" t="str">
+        <x:v>Crema renovadora</x:v>
+      </x:c>
+      <x:c r="D10" s="13" t="str">
+        <x:v>Cremas renovadoras</x:v>
+      </x:c>
+      <x:c r="E10" s="13" t="str">
+        <x:v>Accesorios</x:v>
+      </x:c>
+      <x:c r="F10" s="13" t="str">
+        <x:v>Cuidado</x:v>
+      </x:c>
+      <x:c r="G10" s="13" t="str">
+        <x:v>Sin guia</x:v>
+      </x:c>
+      <x:c r="H10" s="13" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+      <x:c r="I10" s="13" t="str">
         <x:v>Crema renovadora</x:v>
       </x:c>
     </x:row>
@@ -3164,11 +3222,11 @@
     <x:col min="1" max="1" width="7.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="7.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="8.5" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9.75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="41.880001068115234" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="9.5" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="19" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="8.5" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="19.5" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15.5" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="6.75" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="35.25" hidden="0" customWidth="1"/>
   </x:cols>
@@ -3271,7 +3329,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="13" t="n">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B4" s="13" t="str">
         <x:v>Columbia</x:v>
@@ -3280,7 +3338,7 @@
         <x:v>Vestuario</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
-        <x:v>*</x:v>
+        <x:v>Casacas, Polos, Polerones, Camisas, Blusas, Chalecos</x:v>
       </x:c>
       <x:c r="E4" s="13" t="str">
         <x:v>Mujer</x:v>
@@ -3292,18 +3350,18 @@
         <x:v>CLB_MUJER_TOPS</x:v>
       </x:c>
       <x:c r="H4" s="13" t="str">
-        <x:v>Vestuario</x:v>
+        <x:v>Vestuario TOPS</x:v>
       </x:c>
       <x:c r="I4" s="13" t="str">
         <x:v>Activo</x:v>
       </x:c>
       <x:c r="J4" s="13" t="str">
-        <x:v>Marca + categoria + genero</x:v>
+        <x:v>Marca + categoria + genero + tipo TOPS</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="13" t="n">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
         <x:v>Columbia</x:v>
@@ -3312,7 +3370,7 @@
         <x:v>Vestuario</x:v>
       </x:c>
       <x:c r="D5" s="13" t="str">
-        <x:v>*</x:v>
+        <x:v>Casacas, Polos, Polerones, Camisas, Blusas, Chalecos</x:v>
       </x:c>
       <x:c r="E5" s="13" t="str">
         <x:v>Hombre</x:v>
@@ -3324,42 +3382,106 @@
         <x:v>CLB_HOMBRE_TOPS</x:v>
       </x:c>
       <x:c r="H5" s="13" t="str">
-        <x:v>Vestuario</x:v>
+        <x:v>Vestuario TOPS</x:v>
       </x:c>
       <x:c r="I5" s="13" t="str">
         <x:v>Activo</x:v>
       </x:c>
       <x:c r="J5" s="13" t="str">
-        <x:v>Marca + categoria + genero</x:v>
+        <x:v>Marca + categoria + genero + tipo TOPS</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="13" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B6" s="13" t="str">
+        <x:v>Columbia</x:v>
+      </x:c>
+      <x:c r="C6" s="13" t="str">
+        <x:v>Vestuario</x:v>
+      </x:c>
+      <x:c r="D6" s="13" t="str">
+        <x:v>Pantalones, Shorts, Bermudas, Faldas, Leggings, Joggers</x:v>
+      </x:c>
+      <x:c r="E6" s="13" t="str">
+        <x:v>Mujer</x:v>
+      </x:c>
+      <x:c r="F6" s="13" t="str">
+        <x:v>Adulto</x:v>
+      </x:c>
+      <x:c r="G6" s="13" t="str">
+        <x:v>CLB_MUJER_BOTTOMS</x:v>
+      </x:c>
+      <x:c r="H6" s="13" t="str">
+        <x:v>Vestuario BOTTOMS</x:v>
+      </x:c>
+      <x:c r="I6" s="13" t="str">
+        <x:v>Activo</x:v>
+      </x:c>
+      <x:c r="J6" s="13" t="str">
+        <x:v>Marca + categoria + genero + tipo BOTTOMS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B7" s="13" t="str">
+        <x:v>Columbia</x:v>
+      </x:c>
+      <x:c r="C7" s="13" t="str">
+        <x:v>Vestuario</x:v>
+      </x:c>
+      <x:c r="D7" s="13" t="str">
+        <x:v>Pantalones, Shorts, Bermudas, Faldas, Leggings, Joggers</x:v>
+      </x:c>
+      <x:c r="E7" s="13" t="str">
+        <x:v>Hombre</x:v>
+      </x:c>
+      <x:c r="F7" s="13" t="str">
+        <x:v>Adulto</x:v>
+      </x:c>
+      <x:c r="G7" s="13" t="str">
+        <x:v>CLB_HOMBRE_BOTTOMS</x:v>
+      </x:c>
+      <x:c r="H7" s="13" t="str">
+        <x:v>Vestuario BOTTOMS</x:v>
+      </x:c>
+      <x:c r="I7" s="13" t="str">
+        <x:v>Activo</x:v>
+      </x:c>
+      <x:c r="J7" s="13" t="str">
+        <x:v>Marca + categoria + genero + tipo BOTTOMS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="13" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B6" s="13" t="str">
+      <x:c r="B8" s="13" t="str">
         <x:v>*</x:v>
       </x:c>
-      <x:c r="C6" s="13" t="str">
+      <x:c r="C8" s="13" t="str">
         <x:v>Accesorios</x:v>
       </x:c>
-      <x:c r="D6" s="13" t="str">
+      <x:c r="D8" s="13" t="str">
         <x:v>*</x:v>
       </x:c>
-      <x:c r="E6" s="13" t="str">
+      <x:c r="E8" s="13" t="str">
         <x:v>*</x:v>
       </x:c>
-      <x:c r="F6" s="13" t="str">
+      <x:c r="F8" s="13" t="str">
         <x:v>*</x:v>
       </x:c>
-      <x:c r="G6" s="13" t="str"/>
-      <x:c r="H6" s="13" t="str">
+      <x:c r="G8" s="13" t="str"/>
+      <x:c r="H8" s="13" t="str">
         <x:v>Accesorios</x:v>
       </x:c>
-      <x:c r="I6" s="13" t="str">
+      <x:c r="I8" s="13" t="str">
         <x:v>Revision</x:v>
       </x:c>
-      <x:c r="J6" s="13" t="str">
+      <x:c r="J8" s="13" t="str">
         <x:v>No asignar guia automatica si no hay confianza</x:v>
       </x:c>
     </x:row>
@@ -3374,11 +3496,11 @@
   <x:cols>
     <x:col min="1" max="1" width="8.5" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="10.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="8.5" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15.5" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="19.1299991607666" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="10.5" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="13.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="5.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="36.5" hidden="0" customWidth="1"/>
   </x:cols>
@@ -3449,7 +3571,7 @@
         <x:v>Casacas</x:v>
       </x:c>
       <x:c r="C3" s="13" t="str">
-        <x:v>Vestuario</x:v>
+        <x:v>Vestuario TOPS</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
         <x:v>Casacas</x:v>
@@ -3461,7 +3583,7 @@
         <x:v>Adulto/Ninos</x:v>
       </x:c>
       <x:c r="G3" s="13" t="str">
-        <x:v>Guia vestuario</x:v>
+        <x:v>CLB_*_TOPS</x:v>
       </x:c>
       <x:c r="H3" s="13" t="str">
         <x:v>Activo</x:v>
@@ -3478,7 +3600,7 @@
         <x:v>Polos</x:v>
       </x:c>
       <x:c r="C4" s="13" t="str">
-        <x:v>Vestuario</x:v>
+        <x:v>Vestuario TOPS</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
         <x:v>Polos</x:v>
@@ -3490,7 +3612,7 @@
         <x:v>Adulto/Ninos</x:v>
       </x:c>
       <x:c r="G4" s="13" t="str">
-        <x:v>Guia vestuario</x:v>
+        <x:v>CLB_*_TOPS</x:v>
       </x:c>
       <x:c r="H4" s="13" t="str">
         <x:v>Activo</x:v>
@@ -3501,16 +3623,16 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="13" t="str">
-        <x:v>Accesorios</x:v>
+        <x:v>Vestuario</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>Gorros</x:v>
+        <x:v>Pantalones</x:v>
       </x:c>
       <x:c r="C5" s="13" t="str">
-        <x:v>Accesorios</x:v>
+        <x:v>Vestuario BOTTOMS</x:v>
       </x:c>
       <x:c r="D5" s="13" t="str">
-        <x:v>Gorros</x:v>
+        <x:v>Pantalones</x:v>
       </x:c>
       <x:c r="E5" s="13" t="str">
         <x:v>Hombre, Mujer, Unisex</x:v>
@@ -3519,12 +3641,70 @@
         <x:v>Adulto/Ninos</x:v>
       </x:c>
       <x:c r="G5" s="13" t="str">
-        <x:v>Revision</x:v>
+        <x:v>CLB_*_BOTTOMS</x:v>
       </x:c>
       <x:c r="H5" s="13" t="str">
         <x:v>Activo</x:v>
       </x:c>
       <x:c r="I5" s="13" t="str">
+        <x:v>Usar tallas reales de BigQuery</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="13" t="str">
+        <x:v>Vestuario</x:v>
+      </x:c>
+      <x:c r="B6" s="13" t="str">
+        <x:v>Shorts</x:v>
+      </x:c>
+      <x:c r="C6" s="13" t="str">
+        <x:v>Vestuario BOTTOMS</x:v>
+      </x:c>
+      <x:c r="D6" s="13" t="str">
+        <x:v>Shorts</x:v>
+      </x:c>
+      <x:c r="E6" s="13" t="str">
+        <x:v>Hombre, Mujer, Unisex</x:v>
+      </x:c>
+      <x:c r="F6" s="13" t="str">
+        <x:v>Adulto/Ninos</x:v>
+      </x:c>
+      <x:c r="G6" s="13" t="str">
+        <x:v>CLB_*_BOTTOMS</x:v>
+      </x:c>
+      <x:c r="H6" s="13" t="str">
+        <x:v>Activo</x:v>
+      </x:c>
+      <x:c r="I6" s="13" t="str">
+        <x:v>Usar tallas reales de BigQuery</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="13" t="str">
+        <x:v>Accesorios</x:v>
+      </x:c>
+      <x:c r="B7" s="13" t="str">
+        <x:v>Gorros</x:v>
+      </x:c>
+      <x:c r="C7" s="13" t="str">
+        <x:v>Accesorios</x:v>
+      </x:c>
+      <x:c r="D7" s="13" t="str">
+        <x:v>Gorros</x:v>
+      </x:c>
+      <x:c r="E7" s="13" t="str">
+        <x:v>Hombre, Mujer, Unisex</x:v>
+      </x:c>
+      <x:c r="F7" s="13" t="str">
+        <x:v>Adulto/Ninos</x:v>
+      </x:c>
+      <x:c r="G7" s="13" t="str">
+        <x:v>Revision</x:v>
+      </x:c>
+      <x:c r="H7" s="13" t="str">
+        <x:v>Activo</x:v>
+      </x:c>
+      <x:c r="I7" s="13" t="str">
         <x:v>Puede ser talla unica o varias tallas segun fuente</x:v>
       </x:c>
     </x:row>

--- a/outputs/formato_input_catalog_control_center_brand_basico_handle_20260720.xlsx
+++ b/outputs/formato_input_catalog_control_center_brand_basico_handle_20260720.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPUT_COMERCIAL" sheetId="1" r:id="R1d5e45306d944a60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DICCIONARIO_COLUMNAS" sheetId="2" r:id="R2b49714f67a94d2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIPOS_PRENDA" sheetId="3" r:id="R08b199c1dc0c4628"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUIAS_TALLA" sheetId="4" r:id="R29abed733301415e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATEGORIAS" sheetId="5" r:id="R9932a7771e9842fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALORES_PERMITIDOS" sheetId="6" r:id="R15c01aeed0bf4140"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERRORES_Y_ADVERTENCIAS" sheetId="7" r:id="R4c074ce3d2ac44d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPUT_COMERCIAL" sheetId="1" r:id="Ra38dce4017a74eb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DICCIONARIO_COLUMNAS" sheetId="2" r:id="R8ed2565e717240f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIPOS_PRENDA" sheetId="3" r:id="R71a1f937efdc4b40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUIAS_TALLA" sheetId="4" r:id="R4d927292f1b04252"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATEGORIAS" sheetId="5" r:id="R4d3e23983c4a4872"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALORES_PERMITIDOS" sheetId="6" r:id="R46b64637b81d4f3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERRORES_Y_ADVERTENCIAS" sheetId="7" r:id="Rb130d8d0394a4834"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -367,8 +367,8 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="29.1299991607666" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="50.5" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="50.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="11.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="24.3799991607666" hidden="0" customWidth="1"/>
@@ -381,17 +381,17 @@
     <x:col min="13" max="13" width="27.5" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="20.75" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="24.5" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="57" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="48.630001068115234" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="36.25" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="62.25" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="38.25" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="31.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="17" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="28" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="13.5" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="9.25" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="16.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="19.6299991607666" hidden="0" customWidth="1"/>
     <x:col min="22" max="22" width="18.6299991607666" hidden="0" customWidth="1"/>
     <x:col min="23" max="23" width="23" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="43.25" hidden="0" customWidth="1"/>
-    <x:col min="25" max="25" width="56.630001068115234" hidden="0" customWidth="1"/>
-    <x:col min="26" max="26" width="59" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="23.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="27.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="38.25" hidden="0" customWidth="1"/>
     <x:col min="27" max="27" width="15.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="28" max="28" width="19.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="29" max="29" width="16.1299991607666" hidden="0" customWidth="1"/>
@@ -563,7 +563,7 @@
         <x:v>Columbia, Vestuario, Mujer, Casacas</x:v>
       </x:c>
       <x:c r="Z2" s="8" t="str">
-        <x:v>casacas-mujer-columbia-2092991-nry</x:v>
+        <x:v>casaca-impermeable-mujer-arcadia-ii-2092991-nry</x:v>
       </x:c>
       <x:c r="AA2" s="8" t="str"/>
       <x:c r="AB2" s="8" t="str"/>
@@ -577,10 +577,10 @@
         <x:v>Codigo modelo-color. Ej: 2092991-NRY</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
-        <x:v>La app lo puede obtener desde Mod-Col/ARTI. No lo llena la marca.</x:v>
+        <x:v>Modelo sin color.</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>La app lo puede obtener desde Mod-Col/ARTI. No lo llena la marca.</x:v>
+        <x:v>Codigo de color fuente.</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
         <x:v>Marca destino.</x:v>
@@ -619,22 +619,22 @@
         <x:v>Instrucciones de cuidado.</x:v>
       </x:c>
       <x:c r="P3" s="9" t="str">
-        <x:v>La app la obtiene desde BigQuery/ARTI. No inventar ni cargar tallas teoricas.</x:v>
+        <x:v>Talla real. No inventar.</x:v>
       </x:c>
       <x:c r="Q3" s="9" t="str">
-        <x:v>La app lo obtiene desde BigQuery/ARTI. Obligatorio por variante.</x:v>
+        <x:v>Cod Int/SKU obligatorio por variante.</x:v>
       </x:c>
       <x:c r="R3" s="9" t="str">
-        <x:v>La app lo obtiene desde BigQuery/ARTI si existe.</x:v>
+        <x:v>Codigo de barras.</x:v>
       </x:c>
       <x:c r="S3" s="9" t="str">
-        <x:v>La app lo obtiene desde Shopify/ARTI si existe; la marca solo completa si se solicita.</x:v>
+        <x:v>Precio final.</x:v>
       </x:c>
       <x:c r="T3" s="9" t="str">
-        <x:v>Precio antes si aplica desde fuente comercial/ARTI.</x:v>
+        <x:v>Precio antes si aplica.</x:v>
       </x:c>
       <x:c r="U3" s="9" t="str">
-        <x:v>Stock eComm referencial desde BigQuery.</x:v>
+        <x:v>Stock eComm referencial.</x:v>
       </x:c>
       <x:c r="V3" s="9" t="str">
         <x:v>Separar por coma.</x:v>
@@ -643,13 +643,13 @@
         <x:v>Nombre o GID de metaobjeto.</x:v>
       </x:c>
       <x:c r="X3" s="9" t="str">
-        <x:v>La app la resuelve por categoria, tipo de prenda y genero.</x:v>
+        <x:v>Guia Shopify si viene aprobada.</x:v>
       </x:c>
       <x:c r="Y3" s="9" t="str">
-        <x:v>La app los sugiere con marca, categoria, genero, tipo, tecnologia y Mod-Col.</x:v>
+        <x:v>Tags separados por coma.</x:v>
       </x:c>
       <x:c r="Z3" s="9" t="str">
-        <x:v>No llenar manualmente. Formula: tipo de prenda + genero + marca + Mod-Col.</x:v>
+        <x:v>Handle sugerido.</x:v>
       </x:c>
       <x:c r="AA3" s="9" t="str">
         <x:v>Titulo SEO opcional.</x:v>
@@ -2189,10 +2189,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="13.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="9.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="62.25" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="33.630001068115234" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="29.1299991607666" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="38.25" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="14.5" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="23.6299991607666" hidden="0" customWidth="1"/>
   </x:cols>
@@ -2248,13 +2248,13 @@
         <x:v>Codigo modelo</x:v>
       </x:c>
       <x:c r="B3" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>Identificacion</x:v>
       </x:c>
       <x:c r="C3" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
-        <x:v>La app lo puede obtener desde Mod-Col/ARTI. No lo llena la marca.</x:v>
+        <x:v>Modelo sin color.</x:v>
       </x:c>
       <x:c r="E3" s="13" t="str">
         <x:v>2092991</x:v>
@@ -2271,13 +2271,13 @@
         <x:v>Codigo color</x:v>
       </x:c>
       <x:c r="B4" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>Identificacion</x:v>
       </x:c>
       <x:c r="C4" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
-        <x:v>La app lo puede obtener desde Mod-Col/ARTI. No lo llena la marca.</x:v>
+        <x:v>Codigo de color fuente.</x:v>
       </x:c>
       <x:c r="E4" s="13" t="str">
         <x:v>NRY</x:v>
@@ -2568,13 +2568,13 @@
         <x:v>Talla</x:v>
       </x:c>
       <x:c r="B17" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>Variantes y tallas</x:v>
       </x:c>
       <x:c r="C17" s="13" t="str">
         <x:v>SI</x:v>
       </x:c>
       <x:c r="D17" s="13" t="str">
-        <x:v>La app la obtiene desde BigQuery/ARTI. No inventar ni cargar tallas teoricas.</x:v>
+        <x:v>Talla real. No inventar.</x:v>
       </x:c>
       <x:c r="E17" s="13" t="str">
         <x:v>M</x:v>
@@ -2591,13 +2591,13 @@
         <x:v>SKU</x:v>
       </x:c>
       <x:c r="B18" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>Variantes y tallas</x:v>
       </x:c>
       <x:c r="C18" s="13" t="str">
         <x:v>SI</x:v>
       </x:c>
       <x:c r="D18" s="13" t="str">
-        <x:v>La app lo obtiene desde BigQuery/ARTI. Obligatorio por variante.</x:v>
+        <x:v>Cod Int/SKU obligatorio por variante.</x:v>
       </x:c>
       <x:c r="E18" s="13" t="str">
         <x:v>5327440</x:v>
@@ -2614,13 +2614,13 @@
         <x:v>EAN</x:v>
       </x:c>
       <x:c r="B19" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>Variantes y tallas</x:v>
       </x:c>
       <x:c r="C19" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D19" s="13" t="str">
-        <x:v>La app lo obtiene desde BigQuery/ARTI si existe.</x:v>
+        <x:v>Codigo de barras.</x:v>
       </x:c>
       <x:c r="E19" s="13" t="str">
         <x:v>7800000000000</x:v>
@@ -2637,13 +2637,13 @@
         <x:v>Precio</x:v>
       </x:c>
       <x:c r="B20" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>Precios</x:v>
       </x:c>
       <x:c r="C20" s="13" t="str">
         <x:v>SI</x:v>
       </x:c>
       <x:c r="D20" s="13" t="str">
-        <x:v>La app lo obtiene desde Shopify/ARTI si existe; la marca solo completa si se solicita.</x:v>
+        <x:v>Precio final.</x:v>
       </x:c>
       <x:c r="E20" s="13" t="str">
         <x:v>299.90</x:v>
@@ -2660,13 +2660,13 @@
         <x:v>Compare At Price</x:v>
       </x:c>
       <x:c r="B21" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>Precios</x:v>
       </x:c>
       <x:c r="C21" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D21" s="13" t="str">
-        <x:v>Precio antes si aplica desde fuente comercial/ARTI.</x:v>
+        <x:v>Precio antes si aplica.</x:v>
       </x:c>
       <x:c r="E21" s="13" t="str"/>
       <x:c r="F21" s="13" t="str">
@@ -2681,13 +2681,13 @@
         <x:v>Stock disponible</x:v>
       </x:c>
       <x:c r="B22" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>Inventario</x:v>
       </x:c>
       <x:c r="C22" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D22" s="13" t="str">
-        <x:v>Stock eComm referencial desde BigQuery.</x:v>
+        <x:v>Stock eComm referencial.</x:v>
       </x:c>
       <x:c r="E22" s="13" t="str">
         <x:v>12</x:v>
@@ -2750,13 +2750,13 @@
         <x:v>Guia de tallas</x:v>
       </x:c>
       <x:c r="B25" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>Guia de talla</x:v>
       </x:c>
       <x:c r="C25" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D25" s="13" t="str">
-        <x:v>La app la resuelve por categoria, tipo de prenda y genero.</x:v>
+        <x:v>Guia Shopify si viene aprobada.</x:v>
       </x:c>
       <x:c r="E25" s="13" t="str">
         <x:v>CLB_MUJER_TOPS</x:v>
@@ -2773,13 +2773,13 @@
         <x:v>Tags sugeridos</x:v>
       </x:c>
       <x:c r="B26" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>SEO y tags</x:v>
       </x:c>
       <x:c r="C26" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D26" s="13" t="str">
-        <x:v>La app los sugiere con marca, categoria, genero, tipo, tecnologia y Mod-Col.</x:v>
+        <x:v>Tags separados por coma.</x:v>
       </x:c>
       <x:c r="E26" s="13" t="str">
         <x:v>Columbia, Vestuario, Mujer, Casacas</x:v>
@@ -2796,16 +2796,16 @@
         <x:v>Handle sugerido</x:v>
       </x:c>
       <x:c r="B27" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>SEO y tags</x:v>
       </x:c>
       <x:c r="C27" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D27" s="13" t="str">
-        <x:v>No llenar manualmente. Formula: tipo de prenda + genero + marca + Mod-Col.</x:v>
+        <x:v>Handle sugerido.</x:v>
       </x:c>
       <x:c r="E27" s="13" t="str">
-        <x:v>casacas-mujer-columbia-2092991-nry</x:v>
+        <x:v>casaca-impermeable-mujer-arcadia-ii-2092991-nry</x:v>
       </x:c>
       <x:c r="F27" s="13" t="str">
         <x:v>Producto / reporte</x:v>
@@ -2909,13 +2909,13 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22.1299991607666" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="21" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="14.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="15.75" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="8.5" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="10.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="15.5" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="13.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="21" hidden="0" customWidth="1"/>
   </x:cols>
@@ -2998,7 +2998,7 @@
         <x:v>Casacas</x:v>
       </x:c>
       <x:c r="G3" s="13" t="str">
-        <x:v>Vestuario TOPS</x:v>
+        <x:v>Vestuario</x:v>
       </x:c>
       <x:c r="H3" s="13" t="str">
         <x:v>NO</x:v>
@@ -3027,7 +3027,7 @@
         <x:v>Polos</x:v>
       </x:c>
       <x:c r="G4" s="13" t="str">
-        <x:v>Vestuario TOPS</x:v>
+        <x:v>Vestuario</x:v>
       </x:c>
       <x:c r="H4" s="13" t="str">
         <x:v>NO</x:v>
@@ -3038,175 +3038,117 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="13" t="str">
-        <x:v>pantalon, pants, jogger</x:v>
+        <x:v>gorro, beanie, jockey</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>Pantalon</x:v>
+        <x:v>Gorro</x:v>
       </x:c>
       <x:c r="C5" s="13" t="str">
-        <x:v>Pantalon</x:v>
+        <x:v>Gorro</x:v>
       </x:c>
       <x:c r="D5" s="13" t="str">
-        <x:v>Pantalones</x:v>
+        <x:v>Gorros</x:v>
       </x:c>
       <x:c r="E5" s="13" t="str">
-        <x:v>Vestuario</x:v>
+        <x:v>Accesorios</x:v>
       </x:c>
       <x:c r="F5" s="13" t="str">
-        <x:v>Pantalones</x:v>
+        <x:v>Gorros</x:v>
       </x:c>
       <x:c r="G5" s="13" t="str">
-        <x:v>Vestuario BOTTOMS</x:v>
+        <x:v>Accesorios</x:v>
       </x:c>
       <x:c r="H5" s="13" t="str">
-        <x:v>NO</x:v>
+        <x:v>SI</x:v>
       </x:c>
       <x:c r="I5" s="13" t="str">
-        <x:v>Pantalon Trekking Mujer</x:v>
+        <x:v>Gorro Cachalot</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="13" t="str">
-        <x:v>short, shorts, bermuda, falda</x:v>
+        <x:v>mochila, bolso, cartera, bag</x:v>
       </x:c>
       <x:c r="B6" s="13" t="str">
-        <x:v>Short</x:v>
+        <x:v>Bolso</x:v>
       </x:c>
       <x:c r="C6" s="13" t="str">
-        <x:v>Short</x:v>
+        <x:v>Bolso</x:v>
       </x:c>
       <x:c r="D6" s="13" t="str">
-        <x:v>Shorts</x:v>
+        <x:v>Bolsos</x:v>
       </x:c>
       <x:c r="E6" s="13" t="str">
-        <x:v>Vestuario</x:v>
+        <x:v>Accesorios</x:v>
       </x:c>
       <x:c r="F6" s="13" t="str">
-        <x:v>Shorts</x:v>
+        <x:v>Bolsos</x:v>
       </x:c>
       <x:c r="G6" s="13" t="str">
-        <x:v>Vestuario BOTTOMS</x:v>
+        <x:v>Accesorios</x:v>
       </x:c>
       <x:c r="H6" s="13" t="str">
-        <x:v>NO</x:v>
+        <x:v>SI</x:v>
       </x:c>
       <x:c r="I6" s="13" t="str">
-        <x:v>Short Hombre Outdoor</x:v>
+        <x:v>Bolso Outdoor</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="13" t="str">
-        <x:v>gorro, beanie, jockey</x:v>
+        <x:v>slip on, slip-on</x:v>
       </x:c>
       <x:c r="B7" s="13" t="str">
-        <x:v>Gorro</x:v>
+        <x:v>Slip On</x:v>
       </x:c>
       <x:c r="C7" s="13" t="str">
-        <x:v>Gorro</x:v>
+        <x:v>Slip On</x:v>
       </x:c>
       <x:c r="D7" s="13" t="str">
-        <x:v>Gorros</x:v>
+        <x:v>Slip Ons</x:v>
       </x:c>
       <x:c r="E7" s="13" t="str">
-        <x:v>Accesorios</x:v>
+        <x:v>Calzado</x:v>
       </x:c>
       <x:c r="F7" s="13" t="str">
-        <x:v>Gorros</x:v>
+        <x:v>Slip Ons</x:v>
       </x:c>
       <x:c r="G7" s="13" t="str">
-        <x:v>Accesorios</x:v>
+        <x:v>Calzado</x:v>
       </x:c>
       <x:c r="H7" s="13" t="str">
-        <x:v>SI</x:v>
+        <x:v>NO</x:v>
       </x:c>
       <x:c r="I7" s="13" t="str">
-        <x:v>Gorro Cachalot</x:v>
+        <x:v>Slip On Vans</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="13" t="str">
-        <x:v>mochila, bolso, cartera, bag</x:v>
+        <x:v>crema renovadora, cleaner</x:v>
       </x:c>
       <x:c r="B8" s="13" t="str">
-        <x:v>Bolso</x:v>
+        <x:v>Crema renovadora</x:v>
       </x:c>
       <x:c r="C8" s="13" t="str">
-        <x:v>Bolso</x:v>
+        <x:v>Crema renovadora</x:v>
       </x:c>
       <x:c r="D8" s="13" t="str">
-        <x:v>Bolsos</x:v>
+        <x:v>Cremas renovadoras</x:v>
       </x:c>
       <x:c r="E8" s="13" t="str">
         <x:v>Accesorios</x:v>
       </x:c>
       <x:c r="F8" s="13" t="str">
-        <x:v>Bolsos</x:v>
+        <x:v>Cuidado</x:v>
       </x:c>
       <x:c r="G8" s="13" t="str">
-        <x:v>Accesorios</x:v>
+        <x:v>Sin guia</x:v>
       </x:c>
       <x:c r="H8" s="13" t="str">
         <x:v>SI</x:v>
       </x:c>
       <x:c r="I8" s="13" t="str">
-        <x:v>Bolso Outdoor</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="13" t="str">
-        <x:v>slip on, slip-on</x:v>
-      </x:c>
-      <x:c r="B9" s="13" t="str">
-        <x:v>Slip On</x:v>
-      </x:c>
-      <x:c r="C9" s="13" t="str">
-        <x:v>Slip On</x:v>
-      </x:c>
-      <x:c r="D9" s="13" t="str">
-        <x:v>Slip Ons</x:v>
-      </x:c>
-      <x:c r="E9" s="13" t="str">
-        <x:v>Calzado</x:v>
-      </x:c>
-      <x:c r="F9" s="13" t="str">
-        <x:v>Slip Ons</x:v>
-      </x:c>
-      <x:c r="G9" s="13" t="str">
-        <x:v>Calzado</x:v>
-      </x:c>
-      <x:c r="H9" s="13" t="str">
-        <x:v>NO</x:v>
-      </x:c>
-      <x:c r="I9" s="13" t="str">
-        <x:v>Slip On Vans</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="13" t="str">
-        <x:v>crema renovadora, cleaner</x:v>
-      </x:c>
-      <x:c r="B10" s="13" t="str">
-        <x:v>Crema renovadora</x:v>
-      </x:c>
-      <x:c r="C10" s="13" t="str">
-        <x:v>Crema renovadora</x:v>
-      </x:c>
-      <x:c r="D10" s="13" t="str">
-        <x:v>Cremas renovadoras</x:v>
-      </x:c>
-      <x:c r="E10" s="13" t="str">
-        <x:v>Accesorios</x:v>
-      </x:c>
-      <x:c r="F10" s="13" t="str">
-        <x:v>Cuidado</x:v>
-      </x:c>
-      <x:c r="G10" s="13" t="str">
-        <x:v>Sin guia</x:v>
-      </x:c>
-      <x:c r="H10" s="13" t="str">
-        <x:v>SI</x:v>
-      </x:c>
-      <x:c r="I10" s="13" t="str">
         <x:v>Crema renovadora</x:v>
       </x:c>
     </x:row>
@@ -3222,11 +3164,11 @@
     <x:col min="1" max="1" width="7.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="7.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="8.5" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="41.880001068115234" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9.75" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="9.5" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="19.5" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="15.5" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="19" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="8.5" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="6.75" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="35.25" hidden="0" customWidth="1"/>
   </x:cols>
@@ -3329,7 +3271,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="13" t="n">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B4" s="13" t="str">
         <x:v>Columbia</x:v>
@@ -3338,7 +3280,7 @@
         <x:v>Vestuario</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
-        <x:v>Casacas, Polos, Polerones, Camisas, Blusas, Chalecos</x:v>
+        <x:v>*</x:v>
       </x:c>
       <x:c r="E4" s="13" t="str">
         <x:v>Mujer</x:v>
@@ -3350,18 +3292,18 @@
         <x:v>CLB_MUJER_TOPS</x:v>
       </x:c>
       <x:c r="H4" s="13" t="str">
-        <x:v>Vestuario TOPS</x:v>
+        <x:v>Vestuario</x:v>
       </x:c>
       <x:c r="I4" s="13" t="str">
         <x:v>Activo</x:v>
       </x:c>
       <x:c r="J4" s="13" t="str">
-        <x:v>Marca + categoria + genero + tipo TOPS</x:v>
+        <x:v>Marca + categoria + genero</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="13" t="n">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
         <x:v>Columbia</x:v>
@@ -3370,7 +3312,7 @@
         <x:v>Vestuario</x:v>
       </x:c>
       <x:c r="D5" s="13" t="str">
-        <x:v>Casacas, Polos, Polerones, Camisas, Blusas, Chalecos</x:v>
+        <x:v>*</x:v>
       </x:c>
       <x:c r="E5" s="13" t="str">
         <x:v>Hombre</x:v>
@@ -3382,106 +3324,42 @@
         <x:v>CLB_HOMBRE_TOPS</x:v>
       </x:c>
       <x:c r="H5" s="13" t="str">
-        <x:v>Vestuario TOPS</x:v>
+        <x:v>Vestuario</x:v>
       </x:c>
       <x:c r="I5" s="13" t="str">
         <x:v>Activo</x:v>
       </x:c>
       <x:c r="J5" s="13" t="str">
-        <x:v>Marca + categoria + genero + tipo TOPS</x:v>
+        <x:v>Marca + categoria + genero</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="13" t="n">
-        <x:v>95</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B6" s="13" t="str">
-        <x:v>Columbia</x:v>
+        <x:v>*</x:v>
       </x:c>
       <x:c r="C6" s="13" t="str">
-        <x:v>Vestuario</x:v>
+        <x:v>Accesorios</x:v>
       </x:c>
       <x:c r="D6" s="13" t="str">
-        <x:v>Pantalones, Shorts, Bermudas, Faldas, Leggings, Joggers</x:v>
+        <x:v>*</x:v>
       </x:c>
       <x:c r="E6" s="13" t="str">
-        <x:v>Mujer</x:v>
+        <x:v>*</x:v>
       </x:c>
       <x:c r="F6" s="13" t="str">
-        <x:v>Adulto</x:v>
-      </x:c>
-      <x:c r="G6" s="13" t="str">
-        <x:v>CLB_MUJER_BOTTOMS</x:v>
-      </x:c>
+        <x:v>*</x:v>
+      </x:c>
+      <x:c r="G6" s="13" t="str"/>
       <x:c r="H6" s="13" t="str">
-        <x:v>Vestuario BOTTOMS</x:v>
+        <x:v>Accesorios</x:v>
       </x:c>
       <x:c r="I6" s="13" t="str">
-        <x:v>Activo</x:v>
+        <x:v>Revision</x:v>
       </x:c>
       <x:c r="J6" s="13" t="str">
-        <x:v>Marca + categoria + genero + tipo BOTTOMS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="13" t="n">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="B7" s="13" t="str">
-        <x:v>Columbia</x:v>
-      </x:c>
-      <x:c r="C7" s="13" t="str">
-        <x:v>Vestuario</x:v>
-      </x:c>
-      <x:c r="D7" s="13" t="str">
-        <x:v>Pantalones, Shorts, Bermudas, Faldas, Leggings, Joggers</x:v>
-      </x:c>
-      <x:c r="E7" s="13" t="str">
-        <x:v>Hombre</x:v>
-      </x:c>
-      <x:c r="F7" s="13" t="str">
-        <x:v>Adulto</x:v>
-      </x:c>
-      <x:c r="G7" s="13" t="str">
-        <x:v>CLB_HOMBRE_BOTTOMS</x:v>
-      </x:c>
-      <x:c r="H7" s="13" t="str">
-        <x:v>Vestuario BOTTOMS</x:v>
-      </x:c>
-      <x:c r="I7" s="13" t="str">
-        <x:v>Activo</x:v>
-      </x:c>
-      <x:c r="J7" s="13" t="str">
-        <x:v>Marca + categoria + genero + tipo BOTTOMS</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="13" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B8" s="13" t="str">
-        <x:v>*</x:v>
-      </x:c>
-      <x:c r="C8" s="13" t="str">
-        <x:v>Accesorios</x:v>
-      </x:c>
-      <x:c r="D8" s="13" t="str">
-        <x:v>*</x:v>
-      </x:c>
-      <x:c r="E8" s="13" t="str">
-        <x:v>*</x:v>
-      </x:c>
-      <x:c r="F8" s="13" t="str">
-        <x:v>*</x:v>
-      </x:c>
-      <x:c r="G8" s="13" t="str"/>
-      <x:c r="H8" s="13" t="str">
-        <x:v>Accesorios</x:v>
-      </x:c>
-      <x:c r="I8" s="13" t="str">
-        <x:v>Revision</x:v>
-      </x:c>
-      <x:c r="J8" s="13" t="str">
         <x:v>No asignar guia automatica si no hay confianza</x:v>
       </x:c>
     </x:row>
@@ -3496,11 +3374,11 @@
   <x:cols>
     <x:col min="1" max="1" width="8.5" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="10.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="15.5" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8.5" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="19.1299991607666" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="10.5" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="13.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11.5" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="5.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="36.5" hidden="0" customWidth="1"/>
   </x:cols>
@@ -3571,7 +3449,7 @@
         <x:v>Casacas</x:v>
       </x:c>
       <x:c r="C3" s="13" t="str">
-        <x:v>Vestuario TOPS</x:v>
+        <x:v>Vestuario</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
         <x:v>Casacas</x:v>
@@ -3583,7 +3461,7 @@
         <x:v>Adulto/Ninos</x:v>
       </x:c>
       <x:c r="G3" s="13" t="str">
-        <x:v>CLB_*_TOPS</x:v>
+        <x:v>Guia vestuario</x:v>
       </x:c>
       <x:c r="H3" s="13" t="str">
         <x:v>Activo</x:v>
@@ -3600,7 +3478,7 @@
         <x:v>Polos</x:v>
       </x:c>
       <x:c r="C4" s="13" t="str">
-        <x:v>Vestuario TOPS</x:v>
+        <x:v>Vestuario</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
         <x:v>Polos</x:v>
@@ -3612,7 +3490,7 @@
         <x:v>Adulto/Ninos</x:v>
       </x:c>
       <x:c r="G4" s="13" t="str">
-        <x:v>CLB_*_TOPS</x:v>
+        <x:v>Guia vestuario</x:v>
       </x:c>
       <x:c r="H4" s="13" t="str">
         <x:v>Activo</x:v>
@@ -3623,16 +3501,16 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="13" t="str">
-        <x:v>Vestuario</x:v>
+        <x:v>Accesorios</x:v>
       </x:c>
       <x:c r="B5" s="13" t="str">
-        <x:v>Pantalones</x:v>
+        <x:v>Gorros</x:v>
       </x:c>
       <x:c r="C5" s="13" t="str">
-        <x:v>Vestuario BOTTOMS</x:v>
+        <x:v>Accesorios</x:v>
       </x:c>
       <x:c r="D5" s="13" t="str">
-        <x:v>Pantalones</x:v>
+        <x:v>Gorros</x:v>
       </x:c>
       <x:c r="E5" s="13" t="str">
         <x:v>Hombre, Mujer, Unisex</x:v>
@@ -3641,70 +3519,12 @@
         <x:v>Adulto/Ninos</x:v>
       </x:c>
       <x:c r="G5" s="13" t="str">
-        <x:v>CLB_*_BOTTOMS</x:v>
+        <x:v>Revision</x:v>
       </x:c>
       <x:c r="H5" s="13" t="str">
         <x:v>Activo</x:v>
       </x:c>
       <x:c r="I5" s="13" t="str">
-        <x:v>Usar tallas reales de BigQuery</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="13" t="str">
-        <x:v>Vestuario</x:v>
-      </x:c>
-      <x:c r="B6" s="13" t="str">
-        <x:v>Shorts</x:v>
-      </x:c>
-      <x:c r="C6" s="13" t="str">
-        <x:v>Vestuario BOTTOMS</x:v>
-      </x:c>
-      <x:c r="D6" s="13" t="str">
-        <x:v>Shorts</x:v>
-      </x:c>
-      <x:c r="E6" s="13" t="str">
-        <x:v>Hombre, Mujer, Unisex</x:v>
-      </x:c>
-      <x:c r="F6" s="13" t="str">
-        <x:v>Adulto/Ninos</x:v>
-      </x:c>
-      <x:c r="G6" s="13" t="str">
-        <x:v>CLB_*_BOTTOMS</x:v>
-      </x:c>
-      <x:c r="H6" s="13" t="str">
-        <x:v>Activo</x:v>
-      </x:c>
-      <x:c r="I6" s="13" t="str">
-        <x:v>Usar tallas reales de BigQuery</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="13" t="str">
-        <x:v>Accesorios</x:v>
-      </x:c>
-      <x:c r="B7" s="13" t="str">
-        <x:v>Gorros</x:v>
-      </x:c>
-      <x:c r="C7" s="13" t="str">
-        <x:v>Accesorios</x:v>
-      </x:c>
-      <x:c r="D7" s="13" t="str">
-        <x:v>Gorros</x:v>
-      </x:c>
-      <x:c r="E7" s="13" t="str">
-        <x:v>Hombre, Mujer, Unisex</x:v>
-      </x:c>
-      <x:c r="F7" s="13" t="str">
-        <x:v>Adulto/Ninos</x:v>
-      </x:c>
-      <x:c r="G7" s="13" t="str">
-        <x:v>Revision</x:v>
-      </x:c>
-      <x:c r="H7" s="13" t="str">
-        <x:v>Activo</x:v>
-      </x:c>
-      <x:c r="I7" s="13" t="str">
         <x:v>Puede ser talla unica o varias tallas segun fuente</x:v>
       </x:c>
     </x:row>
